--- a/Altium/PCB_Project_ST-LINK/BOM.xlsx
+++ b/Altium/PCB_Project_ST-LINK/BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ST-Link-My-\Altium\PCB_Project_ST-LINK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAB220E-C16D-4610-B646-6F6C7428D899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE50649-EF2C-4E1A-BBEC-328320E6991E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FC07ED83-90F3-4DD7-A2F0-F4E745DEBEED}"/>
+    <workbookView xWindow="22700" yWindow="7890" windowWidth="28800" windowHeight="15460" xr2:uid="{FC07ED83-90F3-4DD7-A2F0-F4E745DEBEED}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -26,10 +26,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -63,9 +60,6 @@
     <t/>
   </si>
   <si>
-    <t>C1, C6</t>
-  </si>
-  <si>
     <t>CAP: 0603</t>
   </si>
   <si>
@@ -75,15 +69,9 @@
     <t>Ceramic capacitor, 0.1μF, X7R, ±10%, 16V, 0603, -55...+125°C</t>
   </si>
   <si>
-    <t>C2, C3, C4, C5, C7</t>
-  </si>
-  <si>
     <t>Ceramic capacitor, 10μF, X7R, ±10%, 50V, 1206, -55...+125°C</t>
   </si>
   <si>
-    <t>C8, C9</t>
-  </si>
-  <si>
     <t>CAP: 1206</t>
   </si>
   <si>
@@ -111,9 +99,6 @@
     <t>Linear voltage regulator</t>
   </si>
   <si>
-    <t>D2</t>
-  </si>
-  <si>
     <t>SOT223</t>
   </si>
   <si>
@@ -132,9 +117,6 @@
     <t>Resistor film, 100R, ±5%, 0603, 0.1W, -55...+125°C</t>
   </si>
   <si>
-    <t>R1, R4, R7, R8</t>
-  </si>
-  <si>
     <t>RES: 0603</t>
   </si>
   <si>
@@ -144,15 +126,9 @@
     <t>Resistor film, 10K, ±5%, 0603, 0.1W, -55...+125°C</t>
   </si>
   <si>
-    <t>R2</t>
-  </si>
-  <si>
     <t>Resistor film, 5.1K, ±5%, 0603, 0.1W, -55...+125°C</t>
   </si>
   <si>
-    <t>R3, R5, R6</t>
-  </si>
-  <si>
     <t>Разъем L-KLS1-5473 / гнездо USB C 3.1 на плату (C8)</t>
   </si>
   <si>
@@ -220,16 +196,357 @@
   </si>
   <si>
     <t>Crystal_HC-49</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C4,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D2</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -598,13 +915,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6B02D5-1C94-4D92-82D7-544FF1B1B15E}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="84.7109375" customWidth="1"/>
-    <col min="2" max="6" width="19.7109375" customWidth="1"/>
+    <col min="1" max="1" width="84.7265625" customWidth="1"/>
+    <col min="2" max="6" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -624,7 +941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -632,99 +949,99 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F2" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F3" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F4" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -732,193 +1049,193 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F10" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F12" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
